--- a/GroceryApplication/src/test/resources/TestDataFile.xlsx
+++ b/GroceryApplication/src/test/resources/TestDataFile.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Obscura\GroceryApplication\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anees\git\LiveProject\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B23985EE-8667-4D86-BA48-C747606740CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25455078-681A-4500-9E01-4B7A66EE5759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="14953" windowHeight="11278" xr2:uid="{35CD6CCA-3B86-4521-9C94-F6DDEF559A57}"/>
   </bookViews>
@@ -44,7 +44,7 @@
     <t>admin</t>
   </si>
   <si>
-    <t>admin1</t>
+    <t>Test12345</t>
   </si>
 </sst>
 </file>
@@ -433,18 +433,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -452,7 +452,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/GroceryApplication/src/test/resources/TestDataFile.xlsx
+++ b/GroceryApplication/src/test/resources/TestDataFile.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anees\git\LiveProject\GroceryApplication\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25455078-681A-4500-9E01-4B7A66EE5759}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E6C13F-5D4C-4A17-983F-0770B48844C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-104" yWindow="-104" windowWidth="14953" windowHeight="11278" xr2:uid="{35CD6CCA-3B86-4521-9C94-F6DDEF559A57}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="14953" windowHeight="11278" activeTab="1" xr2:uid="{35CD6CCA-3B86-4521-9C94-F6DDEF559A57}"/>
   </bookViews>
   <sheets>
     <sheet name="LoginPage" sheetId="1" r:id="rId1"/>
+    <sheet name="HomePage" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,12 +40,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="3">
   <si>
     <t>admin</t>
   </si>
   <si>
     <t>Test12345</t>
+  </si>
+  <si>
+    <t>Aneesh</t>
   </si>
 </sst>
 </file>
@@ -458,4 +462,22 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0294511-9DD8-4197-90ED-F2C415164534}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="13.85"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <v>12345</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>